--- a/src/simulation_results.xlsx
+++ b/src/simulation_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -475,13 +475,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5">
@@ -503,13 +503,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6">
@@ -517,13 +517,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7">
@@ -531,13 +531,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8">
@@ -551,6 +551,20 @@
         <v>0</v>
       </c>
       <c r="D8" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D9" t="n">
         <v>7</v>
       </c>
     </row>
